--- a/TA/TA Hours - Your Name - Spring 2026.xlsx
+++ b/TA/TA Hours - Your Name - Spring 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Desktop\Spring-Semester-\TA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E13487-A3DF-48AD-A1DC-9F65D311E6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFECCC9D-953F-47B9-90F5-F52EEDDDCE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>Time spent TAing for STAT201 Spring 2026</t>
   </si>
@@ -804,7 +804,7 @@
       <c r="A3" s="1"/>
       <c r="B3" s="42" t="str">
         <f>"You have worked "&amp;Q8&amp;" hours this semester and have "&amp;Q9&amp;" hours left to work."</f>
-        <v>You have worked 8 hours this semester and have 142 hours left to work.</v>
+        <v>You have worked 9.5 hours this semester and have 140.5 hours left to work.</v>
       </c>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
@@ -985,27 +985,27 @@
       <c r="M8" s="1"/>
       <c r="N8" s="38">
         <f>SUM(C7:C49)</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="O8" s="7">
         <f ca="1">(TODAY()-(O21))/7</f>
-        <v>3</v>
+        <v>3.2857142857142856</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" ref="P8:P9" ca="1" si="0">N8/O8</f>
-        <v>2.6666666666666665</v>
+        <v>2.8913043478260869</v>
       </c>
       <c r="Q8" s="8">
         <f t="shared" ref="Q8:S8" si="1">ROUND(N8,3)</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>3.286</v>
       </c>
       <c r="S8" s="39">
         <f t="shared" ca="1" si="1"/>
-        <v>2.6669999999999998</v>
+        <v>2.891</v>
       </c>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -1037,27 +1037,27 @@
       <c r="M9" s="1"/>
       <c r="N9" s="38">
         <f>150-N8</f>
-        <v>142</v>
+        <v>140.5</v>
       </c>
       <c r="O9" s="1">
         <f ca="1">(P21-TODAY())/7</f>
-        <v>14.857142857142858</v>
+        <v>14.571428571428571</v>
       </c>
       <c r="P9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5576923076923066</v>
+        <v>9.6421568627450984</v>
       </c>
       <c r="Q9" s="8">
         <f t="shared" ref="Q9:S9" si="2">ROUND(N9,3)</f>
-        <v>142</v>
+        <v>140.5</v>
       </c>
       <c r="R9" s="8">
         <f t="shared" ca="1" si="2"/>
-        <v>14.856999999999999</v>
+        <v>14.571</v>
       </c>
       <c r="S9" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>9.5579999999999998</v>
+        <v>9.6419999999999995</v>
       </c>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -1205,9 +1205,15 @@
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
+      <c r="B14" s="12">
+        <v>46064</v>
+      </c>
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="27"/>
       <c r="G14" s="28"/>
@@ -1233,9 +1239,15 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
+      <c r="B15" s="12">
+        <v>46065</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="11"/>
@@ -21359,11 +21371,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b03d5476-e3b6-4350-8977-e3faba2d8780" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21626,20 +21639,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b03d5476-e3b6-4350-8977-e3faba2d8780" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1E8C7B-E0D5-46DB-B208-FE86B64740ED}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD16D02-3393-4092-A087-238CC6856663}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b03d5476-e3b6-4350-8977-e3faba2d8780"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21664,9 +21674,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD16D02-3393-4092-A087-238CC6856663}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1E8C7B-E0D5-46DB-B208-FE86B64740ED}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b03d5476-e3b6-4350-8977-e3faba2d8780"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>